--- a/projects/unified-order-management-catering/01_Vision&Scope/01.2_RACI.xlsx
+++ b/projects/unified-order-management-catering/01_Vision&Scope/01.2_RACI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Админ\Desktop\Бизнес-системная аналитика\Git\business-analytics-portfolio\projects\unified-order-management-catering\01_Vision&amp;Scope\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8022244-4946-4B1C-B605-4DCD9ACD326C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED0BF56-1EF6-4CF9-B928-B823B78D5945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1740" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RACI" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="32">
   <si>
     <t>Активность / Роль</t>
   </si>
   <si>
-    <t>Заказчик</t>
-  </si>
-  <si>
     <t>PM</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>4. Проектирование ERD / архитектуры</t>
   </si>
   <si>
-    <t>C/R</t>
-  </si>
-  <si>
     <t>5. Разработка backend (MVP)</t>
   </si>
   <si>
@@ -93,15 +87,9 @@
     <t>9. Тестирование E2E и приемочное тестирование</t>
   </si>
   <si>
-    <t>C/I</t>
-  </si>
-  <si>
     <t>10. Запуск пилота / rollout</t>
   </si>
   <si>
-    <t>R/I</t>
-  </si>
-  <si>
     <t>11. Обучение персонала / документация</t>
   </si>
   <si>
@@ -124,6 +112,15 @@
   </si>
   <si>
     <t>RACI (MVP)</t>
+  </si>
+  <si>
+    <t>С</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Заказчик (Директор)</t>
   </si>
 </sst>
 </file>
@@ -508,7 +505,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -519,329 +516,381 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="I3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="I4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="I5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H13" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -857,7 +906,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -870,7 +919,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -883,7 +932,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -896,7 +945,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
